--- a/08_tables/q8_fd_full_correlation_matrix_with_lags.xlsx
+++ b/08_tables/q8_fd_full_correlation_matrix_with_lags.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q8_fd_full_correlation_matrix_with_lags.xlsx
+++ b/08_tables/q8_fd_full_correlation_matrix_with_lags.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,129 +417,129 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>d_i</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>d_P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>d_W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>d_WR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>d_GDP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>d_LS</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>d_UN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>d_SHORTUN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>d_LONGUN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>d_LF</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>d_REER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>d_SH</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>d_i_lag1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>d_P_lag1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>d_W_lag1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>d_WR_lag1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>d_GDP_lag1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>d_LS_lag1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>d_UN_lag1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>d_SHORTUN_lag1</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>d_LONGUN_lag1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>d_LF_lag1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>d_REER_lag1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>d_SH_lag1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>d_i</t>
         </is>
@@ -566,13 +554,13 @@
         <v>0.1233784021501476</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0973912930732871</v>
+        <v>-0.09739129307328709</v>
       </c>
       <c r="F2" t="n">
         <v>0.1251756301178523</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009281689454998627</v>
+        <v>0.009281689454998625</v>
       </c>
       <c r="H2" t="n">
         <v>-0.3226515610967338</v>
@@ -587,22 +575,22 @@
         <v>0.09704298077941299</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0319978782150881</v>
+        <v>-0.03199787821508813</v>
       </c>
       <c r="M2" t="n">
         <v>0.9781443648855318</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04215879211021226</v>
+        <v>0.04215879211021225</v>
       </c>
       <c r="O2" t="n">
         <v>-0.2050649192657165</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.02550785251116247</v>
+        <v>-0.0255078525111625</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.04450748866583598</v>
+        <v>-0.044507488665836</v>
       </c>
       <c r="R2" t="n">
         <v>0.104393632543272</v>
@@ -620,17 +608,17 @@
         <v>-0.09086579737068279</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04872147930039876</v>
+        <v>0.04872147930039878</v>
       </c>
       <c r="X2" t="n">
         <v>0.01740097053851434</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0524190141839245</v>
+        <v>0.05241901418392452</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>d_P</t>
         </is>
@@ -642,31 +630,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06064738586464157</v>
+        <v>0.06064738586464156</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2073638025576764</v>
+        <v>-0.2073638025576765</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02930796125562221</v>
+        <v>-0.0293079612556222</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.006812283716980976</v>
+        <v>-0.006812283716980966</v>
       </c>
       <c r="H3" t="n">
         <v>0.153923052842532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05152655132947774</v>
+        <v>0.05152655132947773</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006976494315327919</v>
+        <v>0.006976494315327902</v>
       </c>
       <c r="K3" t="n">
         <v>0.04979700352162506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05071170528558906</v>
+        <v>0.05071170528558904</v>
       </c>
       <c r="M3" t="n">
         <v>0.1660595773954855</v>
@@ -678,13 +666,13 @@
         <v>0.6827646850104382</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05254651297426682</v>
+        <v>0.0525465129742668</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.1836256048570664</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04157406433169514</v>
+        <v>0.04157406433169513</v>
       </c>
       <c r="S3" t="n">
         <v>-0.02871203464394278</v>
@@ -693,23 +681,23 @@
         <v>0.01389894670775535</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03899465952115254</v>
+        <v>-0.03899465952115253</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.001280592278602442</v>
+        <v>-0.001280592278602433</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09224112036952625</v>
+        <v>0.09224112036952627</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.04338268139764685</v>
+        <v>-0.04338268139764684</v>
       </c>
       <c r="Y3" t="n">
         <v>0.2860346519544821</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>d_W</t>
         </is>
@@ -718,7 +706,7 @@
         <v>0.1233784021501476</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06064738586464157</v>
+        <v>0.06064738586464156</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -727,77 +715,77 @@
         <v>0.3258439101504346</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1681304022627379</v>
+        <v>0.1681304022627378</v>
       </c>
       <c r="G4" t="n">
-        <v>0.230477156290519</v>
+        <v>0.2304771562905189</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04836581829706432</v>
+        <v>-0.04836581829706429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0496778833762178</v>
+        <v>-0.04967788337621779</v>
       </c>
       <c r="J4" t="n">
         <v>-0.06479992046989418</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08955372338473633</v>
+        <v>0.08955372338473634</v>
       </c>
       <c r="L4" t="n">
         <v>0.04885254174740811</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11664156219879</v>
+        <v>0.1166415621987899</v>
       </c>
       <c r="N4" t="n">
         <v>0.1131289442916128</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.005408334634733818</v>
+        <v>-0.005408334634733843</v>
       </c>
       <c r="P4" t="n">
         <v>0.2422681280170468</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09882327162113745</v>
+        <v>0.09882327162113748</v>
       </c>
       <c r="R4" t="n">
         <v>0.1435103827217881</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02290482758514131</v>
+        <v>0.0229048275851413</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1499547005020641</v>
+        <v>-0.1499547005020642</v>
       </c>
       <c r="U4" t="n">
         <v>-0.0508551366577553</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.07452519711565551</v>
+        <v>-0.07452519711565553</v>
       </c>
       <c r="W4" t="n">
         <v>0.01101765454838616</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05052203733782637</v>
+        <v>0.0505220373378264</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08293428589578611</v>
+        <v>0.08293428589578612</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>d_WR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0973912930732871</v>
+        <v>-0.09739129307328709</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2073638025576764</v>
+        <v>-0.2073638025576765</v>
       </c>
       <c r="D5" t="n">
         <v>0.3258439101504346</v>
@@ -818,16 +806,16 @@
         <v>-0.04997926123838933</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.02076107017223323</v>
+        <v>-0.02076107017223325</v>
       </c>
       <c r="K5" t="n">
         <v>0.05372868593729885</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0333566268567328</v>
+        <v>0.03335662685673279</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1010206737836154</v>
+        <v>-0.1010206737836155</v>
       </c>
       <c r="N5" t="n">
         <v>-0.130514874593781</v>
@@ -836,28 +824,28 @@
         <v>-0.1321614517259073</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05669319711580641</v>
+        <v>0.05669319711580643</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3848535994337274</v>
+        <v>0.3848535994337273</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06122959448344761</v>
+        <v>0.06122959448344763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08400417567159646</v>
+        <v>0.08400417567159645</v>
       </c>
       <c r="T5" t="n">
         <v>-0.126355040328218</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.01767088177204237</v>
+        <v>-0.01767088177204238</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0134228836905722</v>
+        <v>-0.01342288369057219</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01986260372893609</v>
+        <v>0.0198626037289361</v>
       </c>
       <c r="X5" t="n">
         <v>0.05570436398964411</v>
@@ -867,7 +855,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>d_GDP</t>
         </is>
@@ -876,10 +864,10 @@
         <v>0.1251756301178523</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.02930796125562221</v>
+        <v>-0.0293079612556222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1681304022627379</v>
+        <v>0.1681304022627378</v>
       </c>
       <c r="E6" t="n">
         <v>0.07878670974613095</v>
@@ -909,56 +897,56 @@
         <v>0.142110476844786</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07376312846608039</v>
+        <v>-0.07376312846608038</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1195201659907927</v>
+        <v>-0.1195201659907926</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0499783481107249</v>
+        <v>0.04997834811072486</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05911512166423665</v>
+        <v>0.05911512166423667</v>
       </c>
       <c r="R6" t="n">
         <v>0.7187271654028434</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.03516475932654383</v>
+        <v>-0.03516475932654384</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.08100700299973124</v>
+        <v>-0.08100700299973122</v>
       </c>
       <c r="U6" t="n">
         <v>-0.1416881115255262</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.03233859843199587</v>
+        <v>-0.03233859843199589</v>
       </c>
       <c r="W6" t="n">
         <v>0.469922928200393</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03860661078871073</v>
+        <v>0.03860661078871074</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.06237241397826825</v>
+        <v>-0.06237241397826823</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>d_LS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009281689454998627</v>
+        <v>0.009281689454998625</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.006812283716980976</v>
+        <v>-0.006812283716980966</v>
       </c>
       <c r="D7" t="n">
-        <v>0.230477156290519</v>
+        <v>0.2304771562905189</v>
       </c>
       <c r="E7" t="n">
         <v>0.3605299917561596</v>
@@ -970,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005184524854238318</v>
+        <v>0.005184524854238313</v>
       </c>
       <c r="I7" t="n">
         <v>0.06782971967200968</v>
@@ -982,7 +970,7 @@
         <v>0.03845562884895033</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1768990317141024</v>
+        <v>0.1768990317141023</v>
       </c>
       <c r="M7" t="n">
         <v>0.003032720932989506</v>
@@ -991,31 +979,31 @@
         <v>0.2217113435186162</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04279541529746307</v>
+        <v>0.04279541529746305</v>
       </c>
       <c r="P7" t="n">
         <v>0.1771386371547203</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3328229199849912</v>
+        <v>0.3328229199849911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07607643780674284</v>
+        <v>0.07607643780674281</v>
       </c>
       <c r="S7" t="n">
         <v>0.2381914430789128</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3194693622546702</v>
+        <v>-0.3194693622546701</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09133399136600831</v>
+        <v>-0.0913339913660083</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1736578881020888</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07606539117545609</v>
+        <v>0.0760653911754561</v>
       </c>
       <c r="X7" t="n">
         <v>0.1890418756899943</v>
@@ -1025,7 +1013,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>d_UN</t>
         </is>
@@ -1037,7 +1025,7 @@
         <v>0.153923052842532</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04836581829706432</v>
+        <v>-0.04836581829706429</v>
       </c>
       <c r="E8" t="n">
         <v>-0.08585355835611154</v>
@@ -1046,7 +1034,7 @@
         <v>-0.2509289979886349</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005184524854238318</v>
+        <v>0.005184524854238313</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1058,34 +1046,34 @@
         <v>0.5757363944434881</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.08311183282987707</v>
+        <v>-0.08311183282987708</v>
       </c>
       <c r="L8" t="n">
         <v>-0.1102606310917635</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2926560595812939</v>
+        <v>-0.2926560595812938</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09492131542562363</v>
+        <v>0.09492131542562365</v>
       </c>
       <c r="O8" t="n">
         <v>0.3544251047336936</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09959723240129102</v>
+        <v>0.09959723240129108</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.06160340816090373</v>
+        <v>-0.06160340816090372</v>
       </c>
       <c r="R8" t="n">
         <v>-0.1618674084437646</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2604276086135354</v>
+        <v>0.2604276086135355</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5512530254233438</v>
+        <v>0.5512530254233439</v>
       </c>
       <c r="U8" t="n">
         <v>0.2283137782084443</v>
@@ -1094,17 +1082,17 @@
         <v>0.2307168352975335</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008159086345857594</v>
+        <v>0.00815908634585759</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01569006328589696</v>
+        <v>0.01569006328589697</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1045057532880535</v>
+        <v>0.1045057532880534</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>d_SHORTUN</t>
         </is>
@@ -1113,10 +1101,10 @@
         <v>-0.2113826920472665</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05152655132947774</v>
+        <v>0.05152655132947773</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0496778833762178</v>
+        <v>-0.04967788337621779</v>
       </c>
       <c r="E9" t="n">
         <v>-0.04997926123838933</v>
@@ -1137,10 +1125,10 @@
         <v>0.4485714169276464</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01743597794070795</v>
+        <v>0.01743597794070796</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06339064929686047</v>
+        <v>0.0633906492968605</v>
       </c>
       <c r="M9" t="n">
         <v>-0.2055639135823203</v>
@@ -1158,13 +1146,13 @@
         <v>-0.0128441451047157</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.05256170284814115</v>
+        <v>-0.05256170284814116</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07675128295950905</v>
+        <v>0.07675128295950906</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.004343857256555215</v>
+        <v>-0.00434385725655522</v>
       </c>
       <c r="U9" t="n">
         <v>0.1430276074868694</v>
@@ -1176,14 +1164,14 @@
         <v>0.14196277878801</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.006449347107878697</v>
+        <v>-0.006449347107878691</v>
       </c>
       <c r="Y9" t="n">
         <v>0.1341666265124641</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>d_LONGUN</t>
         </is>
@@ -1192,13 +1180,13 @@
         <v>-0.2814982954202612</v>
       </c>
       <c r="C10" t="n">
-        <v>0.006976494315327919</v>
+        <v>0.006976494315327902</v>
       </c>
       <c r="D10" t="n">
         <v>-0.06479992046989418</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02076107017223323</v>
+        <v>-0.02076107017223325</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3113555916006835</v>
@@ -1219,7 +1207,7 @@
         <v>-0.07358621639496686</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.029428973815908</v>
+        <v>-0.02942897381590799</v>
       </c>
       <c r="M10" t="n">
         <v>-0.2538240424795091</v>
@@ -1231,7 +1219,7 @@
         <v>0.1594429505950464</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003778136235219402</v>
+        <v>0.003778136235219404</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.03583716573115333</v>
@@ -1240,10 +1228,10 @@
         <v>-0.3627118731619309</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08441546714820648</v>
+        <v>0.0844154671482065</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4608658282929699</v>
+        <v>0.46086582829297</v>
       </c>
       <c r="U10" t="n">
         <v>0.6832296512383247</v>
@@ -1255,14 +1243,14 @@
         <v>0.02293633141090478</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03018072762895231</v>
+        <v>0.03018072762895232</v>
       </c>
       <c r="Y10" t="n">
         <v>-0.1101740011224456</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>d_LF</t>
         </is>
@@ -1274,7 +1262,7 @@
         <v>0.04979700352162506</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08955372338473633</v>
+        <v>0.08955372338473634</v>
       </c>
       <c r="E11" t="n">
         <v>0.05372868593729885</v>
@@ -1286,10 +1274,10 @@
         <v>0.03845562884895033</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08311183282987707</v>
+        <v>-0.08311183282987708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01743597794070795</v>
+        <v>0.01743597794070796</v>
       </c>
       <c r="J11" t="n">
         <v>-0.07358621639496686</v>
@@ -1298,25 +1286,25 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005347647191838004</v>
+        <v>0.005347647191838</v>
       </c>
       <c r="M11" t="n">
         <v>0.1117093683487235</v>
       </c>
       <c r="N11" t="n">
-        <v>0.05655760898133066</v>
+        <v>0.05655760898133067</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.01006813264948953</v>
+        <v>-0.0100681326494895</v>
       </c>
       <c r="P11" t="n">
-        <v>0.05942554258536154</v>
+        <v>0.05942554258536156</v>
       </c>
       <c r="Q11" t="n">
         <v>0.05607448135765607</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6256886325610759</v>
+        <v>0.625688632561076</v>
       </c>
       <c r="S11" t="n">
         <v>-0.01222905673093201</v>
@@ -1331,62 +1319,62 @@
         <v>-0.1236386850326929</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5934463760207263</v>
+        <v>0.5934463760207264</v>
       </c>
       <c r="X11" t="n">
-        <v>0.007403166172941159</v>
+        <v>0.007403166172941148</v>
       </c>
       <c r="Y11" t="n">
         <v>0.07002948009727043</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>d_REER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0319978782150881</v>
+        <v>-0.03199787821508813</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05071170528558906</v>
+        <v>0.05071170528558904</v>
       </c>
       <c r="D12" t="n">
         <v>0.04885254174740811</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0333566268567328</v>
+        <v>0.03335662685673279</v>
       </c>
       <c r="F12" t="n">
         <v>-0.02178917631802946</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1768990317141024</v>
+        <v>0.1768990317141023</v>
       </c>
       <c r="H12" t="n">
         <v>-0.1102606310917635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06339064929686047</v>
+        <v>0.0633906492968605</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.029428973815908</v>
+        <v>-0.02942897381590799</v>
       </c>
       <c r="K12" t="n">
-        <v>0.005347647191838004</v>
+        <v>0.005347647191838</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02935519728902988</v>
+        <v>-0.02935519728902985</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01238418002986773</v>
+        <v>0.01238418002986772</v>
       </c>
       <c r="O12" t="n">
-        <v>0.136419039057899</v>
+        <v>0.1364190390578991</v>
       </c>
       <c r="P12" t="n">
         <v>-0.03525176159392436</v>
@@ -1395,10 +1383,10 @@
         <v>0.02278791406158642</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0217134345517737</v>
+        <v>0.02171343455177369</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.03731343003005173</v>
+        <v>-0.03731343003005171</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0912713423642061</v>
@@ -1410,17 +1398,17 @@
         <v>-0.04736758101710163</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04250558352940503</v>
+        <v>0.04250558352940504</v>
       </c>
       <c r="X12" t="n">
         <v>0.2331071881115031</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.009344879306486642</v>
+        <v>0.009344879306486645</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>d_SH</t>
         </is>
@@ -1432,10 +1420,10 @@
         <v>0.1660595773954855</v>
       </c>
       <c r="D13" t="n">
-        <v>0.11664156219879</v>
+        <v>0.1166415621987899</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1010206737836154</v>
+        <v>-0.1010206737836155</v>
       </c>
       <c r="F13" t="n">
         <v>0.142110476844786</v>
@@ -1444,7 +1432,7 @@
         <v>0.003032720932989506</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2926560595812939</v>
+        <v>-0.2926560595812938</v>
       </c>
       <c r="I13" t="n">
         <v>-0.2055639135823203</v>
@@ -1456,7 +1444,7 @@
         <v>0.1117093683487235</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.02935519728902988</v>
+        <v>-0.02935519728902985</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1471,13 +1459,13 @@
         <v>-0.03678010391089161</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.05213957156622439</v>
+        <v>-0.05213957156622437</v>
       </c>
       <c r="R13" t="n">
         <v>0.1070853539975175</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06691203686124188</v>
+        <v>-0.06691203686124186</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1577870753391424</v>
@@ -1489,7 +1477,7 @@
         <v>-0.08163441260702708</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0611766800396325</v>
+        <v>0.06117668003963248</v>
       </c>
       <c r="X13" t="n">
         <v>0.01437060238891063</v>
@@ -1499,13 +1487,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>d_i_lag1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04215879211021226</v>
+        <v>0.04215879211021225</v>
       </c>
       <c r="C14" t="n">
         <v>0.2667479607058633</v>
@@ -1517,13 +1505,13 @@
         <v>-0.130514874593781</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07376312846608039</v>
+        <v>-0.07376312846608038</v>
       </c>
       <c r="G14" t="n">
         <v>0.2217113435186162</v>
       </c>
       <c r="H14" t="n">
-        <v>0.09492131542562363</v>
+        <v>0.09492131542562365</v>
       </c>
       <c r="I14" t="n">
         <v>0.1457530697008508</v>
@@ -1532,10 +1520,10 @@
         <v>-0.1152434834006564</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05655760898133066</v>
+        <v>0.05655760898133067</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01238418002986773</v>
+        <v>0.01238418002986772</v>
       </c>
       <c r="M14" t="n">
         <v>0.02552366785600879</v>
@@ -1547,19 +1535,19 @@
         <v>0.1469067767103892</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1260299684588453</v>
+        <v>0.1260299684588454</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.09764027987082735</v>
+        <v>-0.09764027987082738</v>
       </c>
       <c r="R14" t="n">
         <v>0.1267742210007213</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008231423126639097</v>
+        <v>0.008231423126639109</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3232148591368553</v>
+        <v>-0.3232148591368552</v>
       </c>
       <c r="U14" t="n">
         <v>-0.2112849552449763</v>
@@ -1568,17 +1556,17 @@
         <v>-0.2812125985948553</v>
       </c>
       <c r="W14" t="n">
-        <v>0.09758625870350096</v>
+        <v>0.09758625870350097</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.03180377325520004</v>
+        <v>-0.03180377325520005</v>
       </c>
       <c r="Y14" t="n">
         <v>0.9800894347451307</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>d_P_lag1</t>
         </is>
@@ -1590,16 +1578,16 @@
         <v>0.6827646850104382</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.005408334634733818</v>
+        <v>-0.005408334634733843</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1321614517259073</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1195201659907927</v>
+        <v>-0.1195201659907926</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04279541529746307</v>
+        <v>0.04279541529746305</v>
       </c>
       <c r="H15" t="n">
         <v>0.3544251047336936</v>
@@ -1611,10 +1599,10 @@
         <v>0.1594429505950464</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01006813264948953</v>
+        <v>-0.0100681326494895</v>
       </c>
       <c r="L15" t="n">
-        <v>0.136419039057899</v>
+        <v>0.1364190390578991</v>
       </c>
       <c r="M15" t="n">
         <v>-0.1742556104325785</v>
@@ -1626,71 +1614,71 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0634879207289412</v>
+        <v>0.06348792072894122</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2072319477673349</v>
+        <v>-0.2072319477673348</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.03279406843256075</v>
+        <v>-0.03279406843256072</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.004570949453530721</v>
+        <v>-0.004570949453530714</v>
       </c>
       <c r="T15" t="n">
         <v>0.1499881842458643</v>
       </c>
       <c r="U15" t="n">
-        <v>0.05157429295689656</v>
+        <v>0.05157429295689655</v>
       </c>
       <c r="V15" t="n">
-        <v>0.002993119990214492</v>
+        <v>0.002993119990214495</v>
       </c>
       <c r="W15" t="n">
         <v>0.04896144742537516</v>
       </c>
       <c r="X15" t="n">
-        <v>0.04938755094371776</v>
+        <v>0.04938755094371775</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1652044768629781</v>
+        <v>0.1652044768629782</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>d_W_lag1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.02550785251116247</v>
+        <v>-0.0255078525111625</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05254651297426682</v>
+        <v>0.0525465129742668</v>
       </c>
       <c r="D16" t="n">
         <v>0.2422681280170468</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05669319711580641</v>
+        <v>0.05669319711580643</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0499783481107249</v>
+        <v>0.04997834811072486</v>
       </c>
       <c r="G16" t="n">
         <v>0.1771386371547203</v>
       </c>
       <c r="H16" t="n">
-        <v>0.09959723240129102</v>
+        <v>0.09959723240129108</v>
       </c>
       <c r="I16" t="n">
         <v>0.06727669059180397</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003778136235219402</v>
+        <v>0.003778136235219404</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05942554258536154</v>
+        <v>0.05942554258536156</v>
       </c>
       <c r="L16" t="n">
         <v>-0.03525176159392436</v>
@@ -1699,10 +1687,10 @@
         <v>-0.03678010391089161</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1260299684588453</v>
+        <v>0.1260299684588454</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0634879207289412</v>
+        <v>0.06348792072894122</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1711,56 +1699,56 @@
         <v>0.3260805978979234</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1591546909262529</v>
+        <v>0.1591546909262528</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2424601612136405</v>
+        <v>0.2424601612136406</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0495511056875692</v>
+        <v>-0.04955110568756919</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.04755207209534657</v>
+        <v>-0.04755207209534655</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.065231148968159</v>
+        <v>-0.06523114896815903</v>
       </c>
       <c r="W16" t="n">
         <v>0.08735602402019915</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04556997684851345</v>
+        <v>0.04556997684851344</v>
       </c>
       <c r="Y16" t="n">
         <v>0.1174908131500954</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>d_WR_lag1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.04450748866583598</v>
+        <v>-0.044507488665836</v>
       </c>
       <c r="C17" t="n">
         <v>-0.1836256048570664</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09882327162113745</v>
+        <v>0.09882327162113748</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3848535994337274</v>
+        <v>0.3848535994337273</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05911512166423665</v>
+        <v>0.05911512166423667</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3328229199849912</v>
+        <v>0.3328229199849911</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06160340816090373</v>
+        <v>-0.06160340816090372</v>
       </c>
       <c r="I17" t="n">
         <v>-0.0128441451047157</v>
@@ -1775,13 +1763,13 @@
         <v>0.02278791406158642</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.05213957156622439</v>
+        <v>-0.05213957156622437</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.09764027987082735</v>
+        <v>-0.09764027987082738</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2072319477673349</v>
+        <v>-0.2072319477673348</v>
       </c>
       <c r="P17" t="n">
         <v>0.3260805978979234</v>
@@ -1796,16 +1784,16 @@
         <v>0.3629892629287713</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.08541373989476546</v>
+        <v>-0.08541373989476549</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.04931187195819733</v>
+        <v>-0.04931187195819732</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.02080248054367199</v>
+        <v>-0.020802480543672</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05351779131012241</v>
+        <v>0.05351779131012242</v>
       </c>
       <c r="X17" t="n">
         <v>0.03272366265425539</v>
@@ -1815,7 +1803,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>d_GDP_lag1</t>
         </is>
@@ -1824,34 +1812,34 @@
         <v>0.104393632543272</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04157406433169514</v>
+        <v>0.04157406433169513</v>
       </c>
       <c r="D18" t="n">
         <v>0.1435103827217881</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06122959448344761</v>
+        <v>0.06122959448344763</v>
       </c>
       <c r="F18" t="n">
         <v>0.7187271654028434</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07607643780674284</v>
+        <v>0.07607643780674281</v>
       </c>
       <c r="H18" t="n">
         <v>-0.1618674084437646</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05256170284814115</v>
+        <v>-0.05256170284814116</v>
       </c>
       <c r="J18" t="n">
         <v>-0.3627118731619309</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6256886325610759</v>
+        <v>0.625688632561076</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0217134345517737</v>
+        <v>0.02171343455177369</v>
       </c>
       <c r="M18" t="n">
         <v>0.1070853539975175</v>
@@ -1860,10 +1848,10 @@
         <v>0.1267742210007213</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.03279406843256075</v>
+        <v>-0.03279406843256072</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1591546909262529</v>
+        <v>0.1591546909262528</v>
       </c>
       <c r="Q18" t="n">
         <v>0.07795515818611401</v>
@@ -1872,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.06246023148095677</v>
+        <v>-0.06246023148095679</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2552984725273357</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4805569674421861</v>
+        <v>-0.480556967442186</v>
       </c>
       <c r="V18" t="n">
         <v>-0.315314032197853</v>
@@ -1887,14 +1875,14 @@
         <v>0.6054838673089192</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.02747767936832748</v>
+        <v>-0.02747767936832747</v>
       </c>
       <c r="Y18" t="n">
         <v>0.1427936696135682</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>d_LS_lag1</t>
         </is>
@@ -1906,58 +1894,58 @@
         <v>-0.02871203464394278</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02290482758514131</v>
+        <v>0.0229048275851413</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08400417567159646</v>
+        <v>0.08400417567159645</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.03516475932654383</v>
+        <v>-0.03516475932654384</v>
       </c>
       <c r="G19" t="n">
         <v>0.2381914430789128</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2604276086135354</v>
+        <v>0.2604276086135355</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07675128295950905</v>
+        <v>0.07675128295950906</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08441546714820648</v>
+        <v>0.0844154671482065</v>
       </c>
       <c r="K19" t="n">
         <v>-0.01222905673093201</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.03731343003005173</v>
+        <v>-0.03731343003005171</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.06691203686124188</v>
+        <v>-0.06691203686124186</v>
       </c>
       <c r="N19" t="n">
-        <v>0.008231423126639097</v>
+        <v>0.008231423126639109</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.004570949453530721</v>
+        <v>-0.004570949453530714</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2424601612136405</v>
+        <v>0.2424601612136406</v>
       </c>
       <c r="Q19" t="n">
         <v>0.3629892629287713</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.06246023148095677</v>
+        <v>-0.06246023148095679</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.009435407704895465</v>
+        <v>0.009435407704895461</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06970732418480341</v>
+        <v>0.0697073241848034</v>
       </c>
       <c r="V19" t="n">
         <v>-0.08129729772610758</v>
@@ -1969,11 +1957,11 @@
         <v>0.1813439967267147</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.001856625565738143</v>
+        <v>0.001856625565738132</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>d_UN_lag1</t>
         </is>
@@ -1985,25 +1973,25 @@
         <v>0.01389894670775535</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1499547005020641</v>
+        <v>-0.1499547005020642</v>
       </c>
       <c r="E20" t="n">
         <v>-0.126355040328218</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.08100700299973124</v>
+        <v>-0.08100700299973122</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3194693622546702</v>
+        <v>-0.3194693622546701</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5512530254233438</v>
+        <v>0.5512530254233439</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.004343857256555215</v>
+        <v>-0.00434385725655522</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4608658282929699</v>
+        <v>0.46086582829297</v>
       </c>
       <c r="K20" t="n">
         <v>-0.1117379080266076</v>
@@ -2015,22 +2003,22 @@
         <v>-0.1577870753391424</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3232148591368553</v>
+        <v>-0.3232148591368552</v>
       </c>
       <c r="O20" t="n">
         <v>0.1499881842458643</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0495511056875692</v>
+        <v>-0.04955110568756919</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.08541373989476546</v>
+        <v>-0.08541373989476549</v>
       </c>
       <c r="R20" t="n">
         <v>-0.2552984725273357</v>
       </c>
       <c r="S20" t="n">
-        <v>0.009435407704895465</v>
+        <v>0.009435407704895461</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2039,7 +2027,7 @@
         <v>0.4021990310418803</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5745905601942739</v>
+        <v>0.574590560194274</v>
       </c>
       <c r="W20" t="n">
         <v>-0.08467144174082934</v>
@@ -2048,11 +2036,11 @@
         <v>-0.11285185990315</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.2968171326503628</v>
+        <v>-0.2968171326503629</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>d_SHORTUN_lag1</t>
         </is>
@@ -2061,19 +2049,19 @@
         <v>-0.1783933775923288</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.03899465952115254</v>
+        <v>-0.03899465952115253</v>
       </c>
       <c r="D21" t="n">
         <v>-0.0508551366577553</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01767088177204237</v>
+        <v>-0.01767088177204238</v>
       </c>
       <c r="F21" t="n">
         <v>-0.1416881115255262</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09133399136600831</v>
+        <v>-0.0913339913660083</v>
       </c>
       <c r="H21" t="n">
         <v>0.2283137782084443</v>
@@ -2097,19 +2085,19 @@
         <v>-0.2112849552449763</v>
       </c>
       <c r="O21" t="n">
-        <v>0.05157429295689656</v>
+        <v>0.05157429295689655</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.04755207209534657</v>
+        <v>-0.04755207209534655</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.04931187195819733</v>
+        <v>-0.04931187195819732</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.4805569674421861</v>
+        <v>-0.480556967442186</v>
       </c>
       <c r="S21" t="n">
-        <v>0.06970732418480341</v>
+        <v>0.0697073241848034</v>
       </c>
       <c r="T21" t="n">
         <v>0.4021990310418803</v>
@@ -2121,7 +2109,7 @@
         <v>0.4488572761384024</v>
       </c>
       <c r="W21" t="n">
-        <v>0.02043419703508827</v>
+        <v>0.02043419703508825</v>
       </c>
       <c r="X21" t="n">
         <v>0.06463794442552527</v>
@@ -2131,7 +2119,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>d_LONGUN_lag1</t>
         </is>
@@ -2140,16 +2128,16 @@
         <v>-0.09086579737068279</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.001280592278602442</v>
+        <v>-0.001280592278602433</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07452519711565551</v>
+        <v>-0.07452519711565553</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0134228836905722</v>
+        <v>-0.01342288369057219</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.03233859843199587</v>
+        <v>-0.03233859843199589</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1736578881020888</v>
@@ -2176,13 +2164,13 @@
         <v>-0.2812125985948553</v>
       </c>
       <c r="O22" t="n">
-        <v>0.002993119990214492</v>
+        <v>0.002993119990214495</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.065231148968159</v>
+        <v>-0.06523114896815903</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.02080248054367199</v>
+        <v>-0.020802480543672</v>
       </c>
       <c r="R22" t="n">
         <v>-0.315314032197853</v>
@@ -2191,7 +2179,7 @@
         <v>-0.08129729772610758</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5745905601942739</v>
+        <v>0.574590560194274</v>
       </c>
       <c r="U22" t="n">
         <v>0.4488572761384024</v>
@@ -2200,41 +2188,41 @@
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.07430685291659453</v>
+        <v>-0.07430685291659454</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.03085896806301772</v>
+        <v>-0.03085896806301771</v>
       </c>
       <c r="Y22" t="n">
         <v>-0.2570379814798364</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>d_LF_lag1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04872147930039876</v>
+        <v>0.04872147930039878</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09224112036952625</v>
+        <v>0.09224112036952627</v>
       </c>
       <c r="D23" t="n">
         <v>0.01101765454838616</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01986260372893609</v>
+        <v>0.0198626037289361</v>
       </c>
       <c r="F23" t="n">
         <v>0.469922928200393</v>
       </c>
       <c r="G23" t="n">
-        <v>0.07606539117545609</v>
+        <v>0.0760653911754561</v>
       </c>
       <c r="H23" t="n">
-        <v>0.008159086345857594</v>
+        <v>0.00815908634585759</v>
       </c>
       <c r="I23" t="n">
         <v>0.14196277878801</v>
@@ -2243,16 +2231,16 @@
         <v>0.02293633141090478</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5934463760207263</v>
+        <v>0.5934463760207264</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04250558352940503</v>
+        <v>0.04250558352940504</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0611766800396325</v>
+        <v>0.06117668003963248</v>
       </c>
       <c r="N23" t="n">
-        <v>0.09758625870350096</v>
+        <v>0.09758625870350097</v>
       </c>
       <c r="O23" t="n">
         <v>0.04896144742537516</v>
@@ -2261,7 +2249,7 @@
         <v>0.08735602402019915</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.05351779131012241</v>
+        <v>0.05351779131012242</v>
       </c>
       <c r="R23" t="n">
         <v>0.6054838673089192</v>
@@ -2273,23 +2261,23 @@
         <v>-0.08467144174082934</v>
       </c>
       <c r="U23" t="n">
-        <v>0.02043419703508827</v>
+        <v>0.02043419703508825</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.07430685291659453</v>
+        <v>-0.07430685291659454</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.001688593336811901</v>
+        <v>0.001688593336811907</v>
       </c>
       <c r="Y23" t="n">
         <v>0.1101882002784108</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>d_REER_lag1</t>
         </is>
@@ -2298,31 +2286,31 @@
         <v>0.01740097053851434</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.04338268139764685</v>
+        <v>-0.04338268139764684</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05052203733782637</v>
+        <v>0.0505220373378264</v>
       </c>
       <c r="E24" t="n">
         <v>0.05570436398964411</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03860661078871073</v>
+        <v>0.03860661078871074</v>
       </c>
       <c r="G24" t="n">
         <v>0.1890418756899943</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01569006328589696</v>
+        <v>0.01569006328589697</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.006449347107878697</v>
+        <v>-0.006449347107878691</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03018072762895231</v>
+        <v>0.03018072762895232</v>
       </c>
       <c r="K24" t="n">
-        <v>0.007403166172941159</v>
+        <v>0.007403166172941148</v>
       </c>
       <c r="L24" t="n">
         <v>0.2331071881115031</v>
@@ -2331,19 +2319,19 @@
         <v>0.01437060238891063</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.03180377325520004</v>
+        <v>-0.03180377325520005</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04938755094371776</v>
+        <v>0.04938755094371775</v>
       </c>
       <c r="P24" t="n">
-        <v>0.04556997684851345</v>
+        <v>0.04556997684851344</v>
       </c>
       <c r="Q24" t="n">
         <v>0.03272366265425539</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.02747767936832748</v>
+        <v>-0.02747767936832747</v>
       </c>
       <c r="S24" t="n">
         <v>0.1813439967267147</v>
@@ -2355,44 +2343,44 @@
         <v>0.06463794442552527</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.03085896806301772</v>
+        <v>-0.03085896806301771</v>
       </c>
       <c r="W24" t="n">
-        <v>0.001688593336811901</v>
+        <v>0.001688593336811907</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.03111444770088528</v>
+        <v>-0.03111444770088527</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>d_SH_lag1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0524190141839245</v>
+        <v>0.05241901418392452</v>
       </c>
       <c r="C25" t="n">
         <v>0.2860346519544821</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08293428589578611</v>
+        <v>0.08293428589578612</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1386471673025255</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.06237241397826825</v>
+        <v>-0.06237241397826823</v>
       </c>
       <c r="G25" t="n">
         <v>0.2150491747088112</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1045057532880535</v>
+        <v>0.1045057532880534</v>
       </c>
       <c r="I25" t="n">
         <v>0.1341666265124641</v>
@@ -2404,7 +2392,7 @@
         <v>0.07002948009727043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009344879306486642</v>
+        <v>0.009344879306486645</v>
       </c>
       <c r="M25" t="n">
         <v>0.04906961594009523</v>
@@ -2413,7 +2401,7 @@
         <v>0.9800894347451307</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1652044768629781</v>
+        <v>0.1652044768629782</v>
       </c>
       <c r="P25" t="n">
         <v>0.1174908131500954</v>
@@ -2425,10 +2413,10 @@
         <v>0.1427936696135682</v>
       </c>
       <c r="S25" t="n">
-        <v>0.001856625565738143</v>
+        <v>0.001856625565738132</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2968171326503628</v>
+        <v>-0.2968171326503629</v>
       </c>
       <c r="U25" t="n">
         <v>-0.2058953395780652</v>
@@ -2440,7 +2428,7 @@
         <v>0.1101882002784108</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.03111444770088528</v>
+        <v>-0.03111444770088527</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
